--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU143"/>
+  <dimension ref="A1:AU144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,22 +3527,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G20">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-09-18 12:00:00</t>
+          <t>2026-09-18 11:00:00</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-18 12:00:00</t>
+          <t>2026-09-18 11:30:00</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-18 12:30:00</t>
+          <t>2026-09-18 12:00:00</t>
         </is>
       </c>
     </row>
@@ -4663,27 +4663,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-09-18 12:45:00</t>
+          <t>2026-09-18 12:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-18 13:00:00</t>
+          <t>2026-09-18 12:30:00</t>
         </is>
       </c>
     </row>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-09-18 13:00:00</t>
+          <t>2026-09-18 12:45:00</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G34">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-09-18 13:30:00</t>
+          <t>2026-09-18 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-18 13:30:00</t>
+          <t>2026-09-18 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G41">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00:00</t>
+          <t>2026-09-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00:00</t>
+          <t>2026-09-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G51">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-09-18 14:30:00</t>
+          <t>2026-09-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-09-18 14:30:00</t>
+          <t>2026-09-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,22 +9232,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G59">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00:00</t>
+          <t>2026-09-18 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00:00</t>
+          <t>2026-09-18 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G67">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G76">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-09-18 15:15:00</t>
+          <t>2026-09-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30:00</t>
+          <t>2026-09-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30:00</t>
+          <t>2026-09-18 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G86">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G88">
@@ -14769,12 +14769,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:00</t>
+          <t>2026-09-18 15:30:00</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:00</t>
+          <t>2026-09-18 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G92">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G95">
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99">
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00:00</t>
+          <t>2026-09-18 15:45:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00:00</t>
+          <t>2026-09-18 15:45:00</t>
         </is>
       </c>
     </row>
@@ -16893,22 +16893,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G105">
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-09-18 17:00:00</t>
+          <t>2026-09-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-09-18 17:00:00</t>
+          <t>2026-09-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -17866,27 +17866,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-09-18 19:30:00</t>
+          <t>2026-09-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18029,27 +18029,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G109">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-09-18 20:00:00</t>
+          <t>2026-09-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G110">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-09-18 20:30:00</t>
+          <t>2026-09-18 19:30:00</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G111">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-09-18 20:30:00</t>
+          <t>2026-09-18 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G112">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-09-18 21:00:00</t>
+          <t>2026-09-18 20:30:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-09-18 21:00:00</t>
+          <t>2026-09-18 20:30:00</t>
         </is>
       </c>
     </row>
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,7 +22598,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G141">
@@ -23413,22 +23413,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="G142">
@@ -23571,156 +23571,319 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>0</v>
+      </c>
+      <c r="R143">
+        <v>0</v>
+      </c>
+      <c r="S143">
+        <v>0</v>
+      </c>
+      <c r="T143">
+        <v>0</v>
+      </c>
+      <c r="U143">
+        <v>0</v>
+      </c>
+      <c r="V143">
+        <v>0</v>
+      </c>
+      <c r="W143">
+        <v>0</v>
+      </c>
+      <c r="X143">
+        <v>0</v>
+      </c>
+      <c r="Y143">
+        <v>0</v>
+      </c>
+      <c r="Z143">
+        <v>0</v>
+      </c>
+      <c r="AA143">
+        <v>0</v>
+      </c>
+      <c r="AB143">
+        <v>0</v>
+      </c>
+      <c r="AC143">
+        <v>0</v>
+      </c>
+      <c r="AD143">
+        <v>0</v>
+      </c>
+      <c r="AE143">
+        <v>0</v>
+      </c>
+      <c r="AF143">
+        <v>0</v>
+      </c>
+      <c r="AG143">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ143">
+        <v>0</v>
+      </c>
+      <c r="AK143">
+        <v>0</v>
+      </c>
+      <c r="AL143">
+        <v>0</v>
+      </c>
+      <c r="AM143">
+        <v>-1</v>
+      </c>
+      <c r="AN143">
+        <v>-1</v>
+      </c>
+      <c r="AO143">
+        <v>-1</v>
+      </c>
+      <c r="AP143">
+        <v>-1</v>
+      </c>
+      <c r="AQ143">
+        <v>0</v>
+      </c>
+      <c r="AR143">
+        <v>0</v>
+      </c>
+      <c r="AS143">
+        <v>0</v>
+      </c>
+      <c r="AT143">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>2026-09-18 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F144" t="inlineStr">
         <is>
           <t>Kansas City</t>
         </is>
       </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
-      <c r="I143">
-        <v>0</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143" t="inlineStr">
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>0</v>
-      </c>
-      <c r="R143">
-        <v>0</v>
-      </c>
-      <c r="S143">
-        <v>0</v>
-      </c>
-      <c r="T143">
-        <v>0</v>
-      </c>
-      <c r="U143">
-        <v>0</v>
-      </c>
-      <c r="V143">
-        <v>0</v>
-      </c>
-      <c r="W143">
-        <v>0</v>
-      </c>
-      <c r="X143">
-        <v>0</v>
-      </c>
-      <c r="Y143">
-        <v>0</v>
-      </c>
-      <c r="Z143">
-        <v>0</v>
-      </c>
-      <c r="AA143">
-        <v>0</v>
-      </c>
-      <c r="AB143">
-        <v>0</v>
-      </c>
-      <c r="AC143">
-        <v>0</v>
-      </c>
-      <c r="AD143">
-        <v>0</v>
-      </c>
-      <c r="AE143">
-        <v>0</v>
-      </c>
-      <c r="AF143">
-        <v>0</v>
-      </c>
-      <c r="AG143">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ143">
-        <v>0</v>
-      </c>
-      <c r="AK143">
-        <v>0</v>
-      </c>
-      <c r="AL143">
-        <v>0</v>
-      </c>
-      <c r="AM143">
-        <v>-1</v>
-      </c>
-      <c r="AN143">
-        <v>-1</v>
-      </c>
-      <c r="AO143">
-        <v>-1</v>
-      </c>
-      <c r="AP143">
-        <v>-1</v>
-      </c>
-      <c r="AQ143">
-        <v>0</v>
-      </c>
-      <c r="AR143">
-        <v>0</v>
-      </c>
-      <c r="AS143">
-        <v>0</v>
-      </c>
-      <c r="AT143">
-        <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>0</v>
+      </c>
+      <c r="R144">
+        <v>0</v>
+      </c>
+      <c r="S144">
+        <v>0</v>
+      </c>
+      <c r="T144">
+        <v>0</v>
+      </c>
+      <c r="U144">
+        <v>0</v>
+      </c>
+      <c r="V144">
+        <v>0</v>
+      </c>
+      <c r="W144">
+        <v>0</v>
+      </c>
+      <c r="X144">
+        <v>0</v>
+      </c>
+      <c r="Y144">
+        <v>0</v>
+      </c>
+      <c r="Z144">
+        <v>0</v>
+      </c>
+      <c r="AA144">
+        <v>0</v>
+      </c>
+      <c r="AB144">
+        <v>0</v>
+      </c>
+      <c r="AC144">
+        <v>0</v>
+      </c>
+      <c r="AD144">
+        <v>0</v>
+      </c>
+      <c r="AE144">
+        <v>0</v>
+      </c>
+      <c r="AF144">
+        <v>0</v>
+      </c>
+      <c r="AG144">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ144">
+        <v>0</v>
+      </c>
+      <c r="AK144">
+        <v>0</v>
+      </c>
+      <c r="AL144">
+        <v>0</v>
+      </c>
+      <c r="AM144">
+        <v>-1</v>
+      </c>
+      <c r="AN144">
+        <v>-1</v>
+      </c>
+      <c r="AO144">
+        <v>-1</v>
+      </c>
+      <c r="AP144">
+        <v>-1</v>
+      </c>
+      <c r="AQ144">
+        <v>0</v>
+      </c>
+      <c r="AR144">
+        <v>0</v>
+      </c>
+      <c r="AS144">
+        <v>0</v>
+      </c>
+      <c r="AT144">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
         <is>
           <t>2026-09-18 23:00:00</t>
         </is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N9">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G19">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G41">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G97">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G99">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G105">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G125">

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G83">

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G43">

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU144"/>
+  <dimension ref="A1:AU136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G36">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G135">
@@ -22430,27 +22430,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G136">
@@ -22580,1310 +22580,6 @@
         <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Greece Super League</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Panaitolikos</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>PAOK</t>
-        </is>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>0</v>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137">
-        <v>0</v>
-      </c>
-      <c r="U137">
-        <v>0</v>
-      </c>
-      <c r="V137">
-        <v>0</v>
-      </c>
-      <c r="W137">
-        <v>0</v>
-      </c>
-      <c r="X137">
-        <v>0</v>
-      </c>
-      <c r="Y137">
-        <v>0</v>
-      </c>
-      <c r="Z137">
-        <v>0</v>
-      </c>
-      <c r="AA137">
-        <v>0</v>
-      </c>
-      <c r="AB137">
-        <v>0</v>
-      </c>
-      <c r="AC137">
-        <v>0</v>
-      </c>
-      <c r="AD137">
-        <v>0</v>
-      </c>
-      <c r="AE137">
-        <v>0</v>
-      </c>
-      <c r="AF137">
-        <v>0</v>
-      </c>
-      <c r="AG137">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-      <c r="AK137">
-        <v>0</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>-1</v>
-      </c>
-      <c r="AN137">
-        <v>-1</v>
-      </c>
-      <c r="AO137">
-        <v>-1</v>
-      </c>
-      <c r="AP137">
-        <v>-1</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Orijent 1919</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Opatija</t>
-        </is>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Karlovac 1919</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Dubrava Zagreb</t>
-        </is>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>-1</v>
-      </c>
-      <c r="AN139">
-        <v>-1</v>
-      </c>
-      <c r="AO139">
-        <v>-1</v>
-      </c>
-      <c r="AP139">
-        <v>-1</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Bijelo Brdo</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Hrvace</t>
-        </is>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>0</v>
-      </c>
-      <c r="R140">
-        <v>0</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140">
-        <v>0</v>
-      </c>
-      <c r="U140">
-        <v>0</v>
-      </c>
-      <c r="V140">
-        <v>0</v>
-      </c>
-      <c r="W140">
-        <v>0</v>
-      </c>
-      <c r="X140">
-        <v>0</v>
-      </c>
-      <c r="Y140">
-        <v>0</v>
-      </c>
-      <c r="Z140">
-        <v>0</v>
-      </c>
-      <c r="AA140">
-        <v>0</v>
-      </c>
-      <c r="AB140">
-        <v>0</v>
-      </c>
-      <c r="AC140">
-        <v>0</v>
-      </c>
-      <c r="AD140">
-        <v>0</v>
-      </c>
-      <c r="AE140">
-        <v>0</v>
-      </c>
-      <c r="AF140">
-        <v>0</v>
-      </c>
-      <c r="AG140">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ140">
-        <v>0</v>
-      </c>
-      <c r="AK140">
-        <v>0</v>
-      </c>
-      <c r="AL140">
-        <v>0</v>
-      </c>
-      <c r="AM140">
-        <v>-1</v>
-      </c>
-      <c r="AN140">
-        <v>-1</v>
-      </c>
-      <c r="AO140">
-        <v>-1</v>
-      </c>
-      <c r="AP140">
-        <v>-1</v>
-      </c>
-      <c r="AQ140">
-        <v>0</v>
-      </c>
-      <c r="AR140">
-        <v>0</v>
-      </c>
-      <c r="AS140">
-        <v>0</v>
-      </c>
-      <c r="AT140">
-        <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>HNK Vukovar 1991</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Jadran LP</t>
-        </is>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>0</v>
-      </c>
-      <c r="R141">
-        <v>0</v>
-      </c>
-      <c r="S141">
-        <v>0</v>
-      </c>
-      <c r="T141">
-        <v>0</v>
-      </c>
-      <c r="U141">
-        <v>0</v>
-      </c>
-      <c r="V141">
-        <v>0</v>
-      </c>
-      <c r="W141">
-        <v>0</v>
-      </c>
-      <c r="X141">
-        <v>0</v>
-      </c>
-      <c r="Y141">
-        <v>0</v>
-      </c>
-      <c r="Z141">
-        <v>0</v>
-      </c>
-      <c r="AA141">
-        <v>0</v>
-      </c>
-      <c r="AB141">
-        <v>0</v>
-      </c>
-      <c r="AC141">
-        <v>0</v>
-      </c>
-      <c r="AD141">
-        <v>0</v>
-      </c>
-      <c r="AE141">
-        <v>0</v>
-      </c>
-      <c r="AF141">
-        <v>0</v>
-      </c>
-      <c r="AG141">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>0</v>
-      </c>
-      <c r="AK141">
-        <v>0</v>
-      </c>
-      <c r="AL141">
-        <v>0</v>
-      </c>
-      <c r="AM141">
-        <v>-1</v>
-      </c>
-      <c r="AN141">
-        <v>-1</v>
-      </c>
-      <c r="AO141">
-        <v>-1</v>
-      </c>
-      <c r="AP141">
-        <v>-1</v>
-      </c>
-      <c r="AQ141">
-        <v>0</v>
-      </c>
-      <c r="AR141">
-        <v>0</v>
-      </c>
-      <c r="AS141">
-        <v>0</v>
-      </c>
-      <c r="AT141">
-        <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Dugopolje</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Dinamo Zagreb II</t>
-        </is>
-      </c>
-      <c r="G142">
-        <v>0</v>
-      </c>
-      <c r="H142">
-        <v>0</v>
-      </c>
-      <c r="I142">
-        <v>0</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <v>0</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>0</v>
-      </c>
-      <c r="R142">
-        <v>0</v>
-      </c>
-      <c r="S142">
-        <v>0</v>
-      </c>
-      <c r="T142">
-        <v>0</v>
-      </c>
-      <c r="U142">
-        <v>0</v>
-      </c>
-      <c r="V142">
-        <v>0</v>
-      </c>
-      <c r="W142">
-        <v>0</v>
-      </c>
-      <c r="X142">
-        <v>0</v>
-      </c>
-      <c r="Y142">
-        <v>0</v>
-      </c>
-      <c r="Z142">
-        <v>0</v>
-      </c>
-      <c r="AA142">
-        <v>0</v>
-      </c>
-      <c r="AB142">
-        <v>0</v>
-      </c>
-      <c r="AC142">
-        <v>0</v>
-      </c>
-      <c r="AD142">
-        <v>0</v>
-      </c>
-      <c r="AE142">
-        <v>0</v>
-      </c>
-      <c r="AF142">
-        <v>0</v>
-      </c>
-      <c r="AG142">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ142">
-        <v>0</v>
-      </c>
-      <c r="AK142">
-        <v>0</v>
-      </c>
-      <c r="AL142">
-        <v>0</v>
-      </c>
-      <c r="AM142">
-        <v>-1</v>
-      </c>
-      <c r="AN142">
-        <v>-1</v>
-      </c>
-      <c r="AO142">
-        <v>-1</v>
-      </c>
-      <c r="AP142">
-        <v>-1</v>
-      </c>
-      <c r="AQ142">
-        <v>0</v>
-      </c>
-      <c r="AR142">
-        <v>0</v>
-      </c>
-      <c r="AS142">
-        <v>0</v>
-      </c>
-      <c r="AT142">
-        <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>São Bernardo</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
-      <c r="I143">
-        <v>0</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>0</v>
-      </c>
-      <c r="R143">
-        <v>0</v>
-      </c>
-      <c r="S143">
-        <v>0</v>
-      </c>
-      <c r="T143">
-        <v>0</v>
-      </c>
-      <c r="U143">
-        <v>0</v>
-      </c>
-      <c r="V143">
-        <v>0</v>
-      </c>
-      <c r="W143">
-        <v>0</v>
-      </c>
-      <c r="X143">
-        <v>0</v>
-      </c>
-      <c r="Y143">
-        <v>0</v>
-      </c>
-      <c r="Z143">
-        <v>0</v>
-      </c>
-      <c r="AA143">
-        <v>0</v>
-      </c>
-      <c r="AB143">
-        <v>0</v>
-      </c>
-      <c r="AC143">
-        <v>0</v>
-      </c>
-      <c r="AD143">
-        <v>0</v>
-      </c>
-      <c r="AE143">
-        <v>0</v>
-      </c>
-      <c r="AF143">
-        <v>0</v>
-      </c>
-      <c r="AG143">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ143">
-        <v>0</v>
-      </c>
-      <c r="AK143">
-        <v>0</v>
-      </c>
-      <c r="AL143">
-        <v>0</v>
-      </c>
-      <c r="AM143">
-        <v>-1</v>
-      </c>
-      <c r="AN143">
-        <v>-1</v>
-      </c>
-      <c r="AO143">
-        <v>-1</v>
-      </c>
-      <c r="AP143">
-        <v>-1</v>
-      </c>
-      <c r="AQ143">
-        <v>0</v>
-      </c>
-      <c r="AR143">
-        <v>0</v>
-      </c>
-      <c r="AS143">
-        <v>0</v>
-      </c>
-      <c r="AT143">
-        <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-      <c r="H144">
-        <v>0</v>
-      </c>
-      <c r="I144">
-        <v>0</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>0</v>
-      </c>
-      <c r="R144">
-        <v>0</v>
-      </c>
-      <c r="S144">
-        <v>0</v>
-      </c>
-      <c r="T144">
-        <v>0</v>
-      </c>
-      <c r="U144">
-        <v>0</v>
-      </c>
-      <c r="V144">
-        <v>0</v>
-      </c>
-      <c r="W144">
-        <v>0</v>
-      </c>
-      <c r="X144">
-        <v>0</v>
-      </c>
-      <c r="Y144">
-        <v>0</v>
-      </c>
-      <c r="Z144">
-        <v>0</v>
-      </c>
-      <c r="AA144">
-        <v>0</v>
-      </c>
-      <c r="AB144">
-        <v>0</v>
-      </c>
-      <c r="AC144">
-        <v>0</v>
-      </c>
-      <c r="AD144">
-        <v>0</v>
-      </c>
-      <c r="AE144">
-        <v>0</v>
-      </c>
-      <c r="AF144">
-        <v>0</v>
-      </c>
-      <c r="AG144">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>0</v>
-      </c>
-      <c r="AK144">
-        <v>0</v>
-      </c>
-      <c r="AL144">
-        <v>0</v>
-      </c>
-      <c r="AM144">
-        <v>-1</v>
-      </c>
-      <c r="AN144">
-        <v>-1</v>
-      </c>
-      <c r="AO144">
-        <v>-1</v>
-      </c>
-      <c r="AP144">
-        <v>-1</v>
-      </c>
-      <c r="AQ144">
-        <v>0</v>
-      </c>
-      <c r="AR144">
-        <v>0</v>
-      </c>
-      <c r="AS144">
-        <v>0</v>
-      </c>
-      <c r="AT144">
-        <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
         <is>
           <t>2026-09-18 23:00:00</t>
         </is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU136"/>
+  <dimension ref="A1:AU135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,22 +3690,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G21">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-18 11:30:00</t>
+          <t>2026-09-18 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-18 12:00:00</t>
+          <t>2026-09-18 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-18 12:00:00</t>
+          <t>2026-09-18 11:30:00</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-09-18 12:30:00</t>
+          <t>2026-09-18 12:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-09-18 12:45:00</t>
+          <t>2026-09-18 12:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-09-18 13:00:00</t>
+          <t>2026-09-18 12:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-09-18 13:00:00</t>
+          <t>2026-09-18 12:45:00</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G38">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-18 13:30:00</t>
+          <t>2026-09-18 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-18 13:30:00</t>
+          <t>2026-09-18 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G43">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00:00</t>
+          <t>2026-09-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-18 14:00:00</t>
+          <t>2026-09-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G53">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-09-18 14:30:00</t>
+          <t>2026-09-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-09-18 14:30:00</t>
+          <t>2026-09-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G61">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00:00</t>
+          <t>2026-09-18 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-18 15:00:00</t>
+          <t>2026-09-18 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Deportivo Alavés W</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Deportivo Alavés W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-09-18 15:15:00</t>
+          <t>2026-09-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30:00</t>
+          <t>2026-09-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-09-18 15:30:00</t>
+          <t>2026-09-18 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G90">
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:00</t>
+          <t>2026-09-18 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-09-18 15:45:00</t>
+          <t>2026-09-18 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15426,22 +15426,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G97">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G101">
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00:00</t>
+          <t>2026-09-18 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-09-18 16:00:00</t>
+          <t>2026-09-18 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G107">
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-09-18 17:00:00</t>
+          <t>2026-09-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G109">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-09-18 17:00:00</t>
+          <t>2026-09-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,27 +18192,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G110">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-09-18 19:30:00</t>
+          <t>2026-09-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G111">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-09-18 20:00:00</t>
+          <t>2026-09-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G112">
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-09-18 20:30:00</t>
+          <t>2026-09-18 19:30:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-09-18 20:30:00</t>
+          <t>2026-09-18 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18844,27 +18844,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-09-18 21:00:00</t>
+          <t>2026-09-18 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-18 21:00:00</t>
+          <t>2026-09-18 20:30:00</t>
         </is>
       </c>
     </row>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G134">
@@ -22267,12 +22267,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G135">
@@ -22417,169 +22417,6 @@
         <v>0</v>
       </c>
       <c r="AU135" t="inlineStr">
-        <is>
-          <t>2026-09-18 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>0</v>
-      </c>
-      <c r="R136">
-        <v>0</v>
-      </c>
-      <c r="S136">
-        <v>0</v>
-      </c>
-      <c r="T136">
-        <v>0</v>
-      </c>
-      <c r="U136">
-        <v>0</v>
-      </c>
-      <c r="V136">
-        <v>0</v>
-      </c>
-      <c r="W136">
-        <v>0</v>
-      </c>
-      <c r="X136">
-        <v>0</v>
-      </c>
-      <c r="Y136">
-        <v>0</v>
-      </c>
-      <c r="Z136">
-        <v>0</v>
-      </c>
-      <c r="AA136">
-        <v>0</v>
-      </c>
-      <c r="AB136">
-        <v>0</v>
-      </c>
-      <c r="AC136">
-        <v>0</v>
-      </c>
-      <c r="AD136">
-        <v>0</v>
-      </c>
-      <c r="AE136">
-        <v>0</v>
-      </c>
-      <c r="AF136">
-        <v>0</v>
-      </c>
-      <c r="AG136">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>0</v>
-      </c>
-      <c r="AK136">
-        <v>0</v>
-      </c>
-      <c r="AL136">
-        <v>0</v>
-      </c>
-      <c r="AM136">
-        <v>-1</v>
-      </c>
-      <c r="AN136">
-        <v>-1</v>
-      </c>
-      <c r="AO136">
-        <v>-1</v>
-      </c>
-      <c r="AP136">
-        <v>-1</v>
-      </c>
-      <c r="AQ136">
-        <v>0</v>
-      </c>
-      <c r="AR136">
-        <v>0</v>
-      </c>
-      <c r="AS136">
-        <v>0</v>
-      </c>
-      <c r="AT136">
-        <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
         <is>
           <t>2026-09-18 23:00:00</t>
         </is>

--- a/jogos_2026-09-18.xlsx
+++ b/jogos_2026-09-18.xlsx
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G39">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G101">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G125">
